--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/phi-4/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="G3">
         <v>29</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>48</v>
       </c>
       <c r="H3">
         <v>426</v>
